--- a/data_ejemplo/mes_actual_hph.xlsx
+++ b/data_ejemplo/mes_actual_hph.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,35 +450,40 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>CORR_PAGO</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>UNIDAD_DESEMPENO</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>CENTRO_COSTO</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>CODIGO_MOVIMIENTO</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>NOMBRE_MOVIMIENTO</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>PORCENTAJE</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>MONTO_PAGO</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>TIPO_PROCESO</t>
         </is>
@@ -502,7 +507,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19.664</t>
+          <t>19.664000</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -515,29 +520,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>Medicina</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>CC-MED</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Sueldo base</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
         <v>2200000</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>ORDINARIO</t>
         </is>
@@ -561,7 +569,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19.664</t>
+          <t>19.664000</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -574,29 +582,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>Medicina</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>CC-MED</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="n">
+        <v>210</v>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Trienios antiguedad</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
         <v>240000</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>ORDINARIO</t>
         </is>
@@ -620,7 +631,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>19.664</t>
+          <t>19.664000</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -633,31 +644,34 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>Medicina</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>CC-MED</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="n">
+        <v>310</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>Experiencia calificada EDF</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>20</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>360000</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>ORDINARIO</t>
         </is>
@@ -681,7 +695,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19.664</t>
+          <t>19.664000</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -694,29 +708,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>Medicina</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>CC-MED</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="n">
+        <v>520</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>Reforzamiento profesional diurno RPD</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
         <v>90000</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>ORDINARIO</t>
         </is>
@@ -740,7 +757,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19.664</t>
+          <t>19.664000</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -753,29 +770,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>P014</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>Urgencia</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>CC-URG</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>Sueldo base</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
         <v>1520000</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>ORDINARIO</t>
         </is>
@@ -799,7 +819,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>19.664</t>
+          <t>19.664000</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -812,31 +832,34 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>P014</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>Urgencia</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>CC-URG</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="n">
+        <v>410</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>Asignacion de estimulo competencias</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>10</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>190000</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>ORDINARIO</t>
         </is>
@@ -860,7 +883,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>15.076</t>
+          <t>15.076000</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -873,29 +896,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>Pediatria</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>CC-PED</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>Sueldo base</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
         <v>1700000</v>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>ORDINARIO</t>
         </is>
@@ -919,7 +945,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19.664</t>
+          <t>19.664000</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -932,29 +958,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>P020</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>Imagenologia</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>CC-IMG</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>Sueldo base</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
         <v>2300000</v>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>ORDINARIO</t>
         </is>
@@ -978,7 +1007,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>19.664</t>
+          <t>19.664000</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -991,31 +1020,34 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>P020</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>Imagenologia</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>CC-IMG</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="n">
+        <v>700</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>Asignacion de responsabilidad</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>15</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>345000</v>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>ORDINARIO</t>
         </is>
@@ -1052,7 +1084,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Columnas usan aliases como CODIGO_MOVIMIENTO y NOMBRE_MOVIMIENTO.</t>
+          <t>Incluye CODIGO_MOVIMIENTO, NOMBRE_MOVIMIENTO, CORR_PAGO y TIPO_PROCESO.</t>
         </is>
       </c>
     </row>
